--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008472774029021725</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>51378262</v>
+        <v>3849328</v>
       </c>
       <c r="L2" t="n">
-        <v>26874639</v>
+        <v>1658570</v>
       </c>
       <c r="M2" t="n">
-        <v>6059446</v>
+        <v>306762</v>
       </c>
       <c r="N2" t="n">
-        <v>226556</v>
+        <v>5588</v>
       </c>
       <c r="O2" t="n">
-        <v>3456451</v>
+        <v>165876</v>
       </c>
       <c r="P2" t="n">
-        <v>1349351</v>
+        <v>10158</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999060034751892</v>
+        <v>0.9999345541000366</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8242737650871277</v>
+        <v>0.7104641199111938</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6847280263900757</v>
+        <v>0.5168473720550537</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6004968881607056</v>
+        <v>0.381516307592392</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1493211388587952</v>
+        <v>0.03810718655586243</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6563965678215027</v>
+        <v>0.3942238688468933</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7762019634246826</v>
+        <v>0.5744175314903259</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002031055628665047</v>
       </c>
       <c r="C3" t="n">
-        <v>2497</v>
+        <v>208</v>
       </c>
       <c r="D3" t="n">
-        <v>51378262</v>
+        <v>3849328</v>
       </c>
       <c r="E3" t="n">
-        <v>8218534</v>
+        <v>1013637</v>
       </c>
       <c r="F3" t="n">
-        <v>299429</v>
+        <v>55162</v>
       </c>
       <c r="G3" t="n">
-        <v>26952</v>
+        <v>5003</v>
       </c>
       <c r="H3" t="n">
-        <v>21015</v>
+        <v>5064</v>
       </c>
       <c r="I3" t="n">
-        <v>1517</v>
+        <v>108</v>
       </c>
       <c r="J3" t="n">
-        <v>120192341</v>
+        <v>10016209</v>
       </c>
       <c r="K3" t="n">
-        <v>125053707</v>
+        <v>9832371</v>
       </c>
       <c r="L3" t="n">
-        <v>144093903</v>
+        <v>11433689</v>
       </c>
       <c r="M3" t="n">
-        <v>180682086</v>
+        <v>14886771</v>
       </c>
       <c r="N3" t="n">
-        <v>193590923</v>
+        <v>16098480</v>
       </c>
       <c r="O3" t="n">
-        <v>188019927</v>
+        <v>15561716</v>
       </c>
       <c r="P3" t="n">
-        <v>193243554</v>
+        <v>16128024</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8570442199707031</v>
+        <v>0.7810328006744385</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6805893778800964</v>
+        <v>0.4957662224769592</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5390083789825439</v>
+        <v>0.3244335651397705</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2110259681940079</v>
+        <v>0.06204132363200188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.564233124256134</v>
+        <v>0.3233488202095032</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5809669494628906</v>
+        <v>0.052347332239151</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03202893469858889</v>
       </c>
       <c r="C4" t="n">
-        <v>316</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>10041782</v>
+        <v>1389318</v>
       </c>
       <c r="E4" t="n">
-        <v>26874639</v>
+        <v>1658570</v>
       </c>
       <c r="F4" t="n">
-        <v>2151179</v>
+        <v>235222</v>
       </c>
       <c r="G4" t="n">
-        <v>156539</v>
+        <v>24041</v>
       </c>
       <c r="H4" t="n">
-        <v>236648</v>
+        <v>37181</v>
       </c>
       <c r="I4" t="n">
-        <v>26200</v>
+        <v>1131</v>
       </c>
       <c r="J4" t="n">
-        <v>7123</v>
+        <v>413</v>
       </c>
       <c r="K4" t="n">
-        <v>10953287</v>
+        <v>1568719</v>
       </c>
       <c r="L4" t="n">
-        <v>12373994</v>
+        <v>1550443</v>
       </c>
       <c r="M4" t="n">
-        <v>4031274</v>
+        <v>497298</v>
       </c>
       <c r="N4" t="n">
-        <v>1290684</v>
+        <v>141051</v>
       </c>
       <c r="O4" t="n">
-        <v>1809346</v>
+        <v>254890</v>
       </c>
       <c r="P4" t="n">
-        <v>389051</v>
+        <v>7526</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999529719352722</v>
+        <v>0.9999672770500183</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8403396010398865</v>
+        <v>0.7440789937973022</v>
       </c>
       <c r="S4" t="n">
-        <v>0.682652473449707</v>
+        <v>0.5060874223709106</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5680936574935913</v>
+        <v>0.3506670892238617</v>
       </c>
       <c r="U4" t="n">
-        <v>0.174890473484993</v>
+        <v>0.04721428826451302</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6068354249000549</v>
+        <v>0.3552861511707306</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6645417213439941</v>
+        <v>0.09595057368278503</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2275</v>
+        <v>175</v>
       </c>
       <c r="D5" t="n">
-        <v>652341</v>
+        <v>131953</v>
       </c>
       <c r="E5" t="n">
-        <v>3309161</v>
+        <v>386824</v>
       </c>
       <c r="F5" t="n">
-        <v>6059446</v>
+        <v>306762</v>
       </c>
       <c r="G5" t="n">
-        <v>412573</v>
+        <v>37099</v>
       </c>
       <c r="H5" t="n">
-        <v>719994</v>
+        <v>80341</v>
       </c>
       <c r="I5" t="n">
-        <v>86050</v>
+        <v>2377</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8569944</v>
+        <v>1079182</v>
       </c>
       <c r="L5" t="n">
-        <v>12612664</v>
+        <v>1686898</v>
       </c>
       <c r="M5" t="n">
-        <v>5182394</v>
+        <v>638769</v>
       </c>
       <c r="N5" t="n">
-        <v>847037</v>
+        <v>84481</v>
       </c>
       <c r="O5" t="n">
-        <v>2669476</v>
+        <v>347118</v>
       </c>
       <c r="P5" t="n">
-        <v>973244</v>
+        <v>183892</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999963641166687</v>
+        <v>0.9999747276306152</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9003689289093018</v>
+        <v>0.837846577167511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8724879026412964</v>
+        <v>0.801750123500824</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9529807567596436</v>
+        <v>0.9304289817810059</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9890907406806946</v>
+        <v>0.9861887693405151</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9771436452865601</v>
+        <v>0.9631339311599731</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9930479526519775</v>
+        <v>0.9882778525352478</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>182836</v>
+        <v>22852</v>
       </c>
       <c r="E6" t="n">
-        <v>270744</v>
+        <v>28607</v>
       </c>
       <c r="F6" t="n">
-        <v>273799</v>
+        <v>24406</v>
       </c>
       <c r="G6" t="n">
-        <v>226556</v>
+        <v>5588</v>
       </c>
       <c r="H6" t="n">
-        <v>107979</v>
+        <v>8344</v>
       </c>
       <c r="I6" t="n">
-        <v>11302</v>
+        <v>251</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>71249</v>
+        <v>22349</v>
       </c>
       <c r="E7" t="n">
-        <v>518700</v>
+        <v>106639</v>
       </c>
       <c r="F7" t="n">
-        <v>1188366</v>
+        <v>154860</v>
       </c>
       <c r="G7" t="n">
-        <v>626819</v>
+        <v>59609</v>
       </c>
       <c r="H7" t="n">
-        <v>3456451</v>
+        <v>165876</v>
       </c>
       <c r="I7" t="n">
-        <v>263982</v>
+        <v>3659</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1298</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>5079</v>
+        <v>2247</v>
       </c>
       <c r="E8" t="n">
-        <v>56855</v>
+        <v>14736</v>
       </c>
       <c r="F8" t="n">
-        <v>118501</v>
+        <v>27648</v>
       </c>
       <c r="G8" t="n">
-        <v>67801</v>
+        <v>15299</v>
       </c>
       <c r="H8" t="n">
-        <v>723710</v>
+        <v>123960</v>
       </c>
       <c r="I8" t="n">
-        <v>1349351</v>
+        <v>10158</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
